--- a/target/test-classes/excelfile/Customeraccount.xlsx
+++ b/target/test-classes/excelfile/Customeraccount.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cecilia\playwright_learning\DataDrivenProject\src\test\java\utilities\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cecilia\playwright_learning\DemoDataDrivenProject\src\test\java\excelfile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9107FDC9-0AF4-4916-A496-FF7628F7D95D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F3B9023-5E4A-4D22-B728-71F3E1EEFEF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5544" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2496" yWindow="3360" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCase" sheetId="1" r:id="rId1"/>
@@ -29,23 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
-  <si>
-    <t>Cecilia</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>firstname</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sze</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Chan</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="13">
   <si>
     <t>runmode</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -59,44 +43,41 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>GOGO</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>lastname</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mary</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cheng</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HAHA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HU</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>balance</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>change</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CustomerAccountTest</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>DespoiteTest</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WithdrawnTest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>add</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>withdraw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hermoine Granger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Harry Potter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Neville Longbottom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>browser</t>
+  </si>
+  <si>
+    <t>chrome</t>
+  </si>
+  <si>
+    <t>firefox</t>
   </si>
 </sst>
 </file>
@@ -429,26 +410,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -467,101 +448,110 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3">
-        <v>4939350405</v>
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>4000</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>9000</v>
+      </c>
+      <c r="D4" t="s">
         <v>11</v>
-      </c>
-      <c r="D4">
-        <v>9349935934</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>545353</v>
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>300</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
         <v>6</v>
       </c>
-      <c r="C8" t="s">
-        <v>14</v>
+      <c r="D8" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C9">
         <v>300</v>
       </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C10">
-        <v>-200</v>
+        <v>200</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
